--- a/data/dividends_info_20260914.xlsx
+++ b/data/dividends_info_20260914.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>41.59999847412109</v>
+        <v>41.73500061035156</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2163461617816837</v>
+        <v>0.2156463368486863</v>
       </c>
       <c r="J2" t="n">
         <v>182</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>64.55000305175781</v>
+        <v>65</v>
       </c>
       <c r="I3" t="n">
-        <v>1.084430622627117</v>
+        <v>1.076923076923077</v>
       </c>
       <c r="J3" t="n">
         <v>161</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8.899999618530273</v>
+        <v>9.020000457763672</v>
       </c>
       <c r="I4" t="n">
-        <v>0.674157332266361</v>
+        <v>0.6651884363083036</v>
       </c>
       <c r="J4" t="n">
         <v>91</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.550000011920929</v>
+        <v>0.5400000214576721</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7272727115095158</v>
+        <v>0.7407407113063494</v>
       </c>
       <c r="J5" t="n">
         <v>91</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>41.59999847412109</v>
+        <v>41.73500061035156</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2163461617816837</v>
+        <v>0.2156463368486863</v>
       </c>
       <c r="J6" t="n">
         <v>91</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.099999904632568</v>
+        <v>2.095000028610229</v>
       </c>
       <c r="I7" t="n">
-        <v>3.666666833181238</v>
+        <v>3.675417610904753</v>
       </c>
       <c r="J7" t="n">
         <v>70</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>24.14500045776367</v>
+        <v>24.01000022888184</v>
       </c>
       <c r="I8" t="n">
-        <v>1.118243921644587</v>
+        <v>1.124531434511253</v>
       </c>
       <c r="J8" t="n">
         <v>70</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>24.70000076293945</v>
+        <v>23.67000007629395</v>
       </c>
       <c r="I9" t="n">
-        <v>2.388663893829719</v>
+        <v>2.492606667081926</v>
       </c>
       <c r="J9" t="n">
         <v>70</v>
@@ -898,12 +898,8 @@
           <t>IT0005312027</t>
         </is>
       </c>
-      <c r="H10" t="n">
-        <v>5.840000152587891</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3.424657444766908</v>
-      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
         <v>63</v>
       </c>
@@ -946,10 +942,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10.44999980926514</v>
+        <v>10.51000022888184</v>
       </c>
       <c r="I11" t="n">
-        <v>4.401913955942436</v>
+        <v>4.376783919908055</v>
       </c>
       <c r="J11" t="n">
         <v>42</v>
@@ -1040,10 +1036,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.550000011920929</v>
+        <v>0.5400000214576721</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7272727115095158</v>
+        <v>0.7407407113063494</v>
       </c>
       <c r="J13" t="n">
         <v>35</v>
@@ -1181,10 +1177,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>24.14500045776367</v>
+        <v>24.01000022888184</v>
       </c>
       <c r="I16" t="n">
-        <v>1.118243921644587</v>
+        <v>1.124531434511253</v>
       </c>
       <c r="J16" t="n">
         <v>7</v>
@@ -1228,10 +1224,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.884999990463257</v>
+        <v>1.894000053405762</v>
       </c>
       <c r="I17" t="n">
-        <v>3.023872694343712</v>
+        <v>3.009503611021736</v>
       </c>
       <c r="J17" t="n">
         <v>7</v>
@@ -1275,10 +1271,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>41.59999847412109</v>
+        <v>41.73500061035156</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2163461617816837</v>
+        <v>0.2156463368486863</v>
       </c>
       <c r="J18" t="n">
         <v>7</v>
@@ -1322,10 +1318,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>97.09999847412109</v>
+        <v>96.09999847412109</v>
       </c>
       <c r="I19" t="n">
-        <v>1.36972195767281</v>
+        <v>1.383975047989369</v>
       </c>
       <c r="J19" t="n">
         <v>7</v>
@@ -1369,10 +1365,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5.960000038146973</v>
+        <v>5.920000076293945</v>
       </c>
       <c r="I20" t="n">
-        <v>5.03355701476259</v>
+        <v>5.067567502259338</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1416,10 +1412,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.550000011920929</v>
+        <v>0.5400000214576721</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7272727115095158</v>
+        <v>0.7407407113063494</v>
       </c>
       <c r="J21" t="n">
         <v>-21</v>
@@ -1479,7 +1475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sesa S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1489,14 +1485,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1506,14 +1502,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1530,7 +1526,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I GRANDI VIAGGI S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1540,14 +1536,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sesa S.p.A.</t>
+          <t>I GRANDI VIAGGI S.p.A.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1564,7 +1560,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1581,7 +1577,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1591,14 +1587,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>Sesa S.p.A.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1608,14 +1604,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>Sesa S.p.A.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1625,14 +1621,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>S.S. Lazio S.p.A.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1642,14 +1638,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>MB Annual Report</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>NEUROSOFT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1666,7 +1662,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1683,7 +1679,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NEUROSOFT</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1700,7 +1696,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S.S. Lazio S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1710,14 +1706,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MB Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1734,7 +1730,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1744,7 +1740,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1757,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1781,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1836,7 +1832,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1846,14 +1842,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1863,7 +1859,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1944,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -1965,14 +1961,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RT&amp;L S.P.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1989,7 +1985,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>I.CO.P. S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2006,7 +2002,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
+          <t>RT&amp;L S.P.A.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2125,7 +2121,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2210,7 +2206,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2227,7 +2223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2261,7 +2257,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>ENTERA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2278,7 +2274,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ENTERA</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2288,7 +2284,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2301,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2342,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2363,7 +2359,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2373,14 +2369,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2397,7 +2393,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2414,7 +2410,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2431,7 +2427,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2448,7 +2444,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2458,14 +2454,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2482,7 +2478,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2499,7 +2495,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>JUVENTUS F.C. S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2509,14 +2505,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2533,7 +2529,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2550,7 +2546,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>JUVENTUS F.C. S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2560,14 +2556,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2577,14 +2573,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2601,7 +2597,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>E-NOVIA S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2618,7 +2614,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>E-NOVIA S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2635,7 +2631,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2652,7 +2648,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2662,14 +2658,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2686,7 +2682,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2703,7 +2699,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2720,7 +2716,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2737,7 +2733,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2754,7 +2750,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2771,7 +2767,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2788,7 +2784,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2805,7 +2801,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2822,7 +2818,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2832,7 +2828,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2852,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2866,7 +2862,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2886,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2907,7 +2903,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2924,7 +2920,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BESTBE HOLDING S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2934,14 +2930,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2958,7 +2954,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2968,14 +2964,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2992,7 +2988,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3009,7 +3005,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3026,7 +3022,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3043,7 +3039,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3060,7 +3056,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3077,7 +3073,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3111,7 +3107,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3128,7 +3124,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3145,7 +3141,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3162,7 +3158,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3179,7 +3175,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3196,7 +3192,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3213,7 +3209,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3230,7 +3226,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3247,7 +3243,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Simone S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3264,7 +3260,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3281,7 +3277,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3298,7 +3294,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3315,7 +3311,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3332,7 +3328,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3349,7 +3345,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3366,7 +3362,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3383,7 +3379,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3400,7 +3396,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3417,7 +3413,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3427,14 +3423,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>DBA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3451,7 +3447,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3468,7 +3464,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3485,7 +3481,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3495,14 +3491,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3512,14 +3508,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>DBA GROUP S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3529,14 +3525,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Guidotti Ships S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3546,14 +3542,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3563,14 +3559,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>Confinvest Oro S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3587,7 +3583,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3597,14 +3593,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3614,14 +3610,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3631,14 +3627,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Guidotti Ships S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3648,14 +3644,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Confinvest Oro S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3672,7 +3668,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3689,7 +3685,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3699,14 +3695,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3716,14 +3712,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3740,7 +3736,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3757,7 +3753,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3774,7 +3770,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3791,7 +3787,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3808,7 +3804,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3825,7 +3821,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3842,7 +3838,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3852,14 +3848,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3876,7 +3872,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>ETI S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3893,7 +3889,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>EPH INVEST S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3910,7 +3906,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3927,7 +3923,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3937,14 +3933,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3961,7 +3957,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3978,7 +3974,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3995,7 +3991,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4012,7 +4008,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4029,7 +4025,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>Adventure S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4046,7 +4042,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Adventure S.p.A.</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4063,7 +4059,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4073,14 +4069,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4097,7 +4093,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4114,7 +4110,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4131,7 +4127,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4148,7 +4144,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Gens Aurea S.p.A.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4165,7 +4161,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>Rocket Sharing Company S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4182,7 +4178,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>TESSELLIS S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4199,7 +4195,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4216,7 +4212,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4226,14 +4222,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4250,7 +4246,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4267,7 +4263,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4284,7 +4280,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>TESSELLIS S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4301,7 +4297,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4318,7 +4314,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4335,7 +4331,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4352,7 +4348,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4369,7 +4365,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Rocket Sharing Company S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4386,7 +4382,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4403,7 +4399,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4420,7 +4416,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4437,7 +4433,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4454,7 +4450,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4471,7 +4467,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4488,7 +4484,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ETI S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4505,7 +4501,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4522,7 +4518,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4539,7 +4535,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>EPH INVEST S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4556,7 +4552,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4573,7 +4569,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4583,14 +4579,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4607,7 +4603,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4624,7 +4620,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4641,7 +4637,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4658,7 +4654,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4675,7 +4671,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Gens Aurea S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4692,7 +4688,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4709,7 +4705,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4726,7 +4722,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4743,7 +4739,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4760,7 +4756,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Dipietro Group S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4770,14 +4766,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4794,7 +4790,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4811,7 +4807,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4828,7 +4824,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>Cube Labs S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4845,7 +4841,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>MEVIM S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4862,7 +4858,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4879,7 +4875,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4896,7 +4892,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4913,7 +4909,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>MEVIM S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -4930,7 +4926,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Cube Labs S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -4947,7 +4943,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -4964,7 +4960,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -4981,7 +4977,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -4998,7 +4994,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Dipietro Group S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5015,7 +5011,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5032,7 +5028,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5049,7 +5045,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5066,7 +5062,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5083,7 +5079,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5100,7 +5096,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5134,7 +5130,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5151,7 +5147,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5168,7 +5164,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5185,7 +5181,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5195,14 +5191,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>First Point S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5219,7 +5215,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5236,7 +5232,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5253,7 +5249,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Portobello S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5270,7 +5266,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5287,7 +5283,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5304,7 +5300,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>Officina Stellare S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5321,7 +5317,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>OPT S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5338,7 +5334,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5348,14 +5344,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Met.Extra Group S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5372,7 +5368,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5382,14 +5378,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5406,7 +5402,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5423,7 +5419,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5440,7 +5436,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5457,7 +5453,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5474,7 +5470,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -5491,7 +5487,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Alia Mentis S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5508,7 +5504,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>B.F. S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -5525,7 +5521,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -5542,7 +5538,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -5559,7 +5555,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -5576,7 +5572,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>First Point S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -5593,7 +5589,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -5610,7 +5606,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Met.Extra Group S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -5627,7 +5623,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -5637,14 +5633,14 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>OPT S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -5661,7 +5657,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Officina Stellare S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -5671,14 +5667,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -5695,7 +5691,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -5712,7 +5708,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -5729,7 +5725,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>B.F. S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -5746,7 +5742,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Alia Mentis S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -5763,7 +5759,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -5780,7 +5776,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -5797,7 +5793,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -5831,7 +5827,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>LANDI RENZO S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -5841,14 +5837,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>S.S. Lazio S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -5858,14 +5854,14 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>SB Annual Report</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -5882,7 +5878,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>S.S. Lazio S.p.A.</t>
+          <t>LANDI RENZO S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -5892,7 +5888,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>SB Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -5916,7 +5912,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -5926,14 +5922,14 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -5943,14 +5939,14 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -5960,14 +5956,14 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -5977,14 +5973,14 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -5994,14 +5990,14 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -6011,14 +6007,14 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -6028,14 +6024,14 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -6107,61 +6103,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Cementir Holding N.V.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ECOSUNTEK S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>